--- a/excelDataSource/20260612_涨停复盘_verified.xlsx
+++ b/excelDataSource/20260612_涨停复盘_verified.xlsx
@@ -3662,17 +3662,17 @@
           <t>迪生力</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
         <is>
           <t>1/4天2板</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
+      <c r="F82" t="inlineStr">
         <is>
           <t>收购全芯半导体30%股权</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>板块标题全部识别成功，各板块声明数量与提取股票数一致，自动校验通过。</t>
+          <t>03/04均识别成功，板块标题与声明数量校验通过。</t>
         </is>
       </c>
     </row>

--- a/excelDataSource/20260612_涨停复盘_verified.xlsx
+++ b/excelDataSource/20260612_涨停复盘_verified.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24220" windowHeight="9880" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03提取" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04提取" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="03提取" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="04提取" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
